--- a/00.xlsx
+++ b/00.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B713D5D-D366-465A-89EB-F10F4873C16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61BAB51D-3CC0-4935-9D05-C300E55EB846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>교시</t>
   </si>
@@ -48,34 +48,39 @@
     <t>1(08:20)</t>
   </si>
   <si>
-    <t>역학</t>
-  </si>
-  <si>
     <t>2(09:20)</t>
   </si>
   <si>
-    <t>3(10:20)</t>
-  </si>
-  <si>
-    <t>4(11:20)</t>
-  </si>
-  <si>
-    <t>통과A</t>
+    <t>6(14:00)</t>
+  </si>
+  <si>
+    <t>7(15:00)</t>
+  </si>
+  <si>
+    <t>8(16:00)</t>
+  </si>
+  <si>
+    <t>화학2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>감독</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3(10:40)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공통영어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4(11:50)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>5(13:00)</t>
-  </si>
-  <si>
-    <t>6(14:00)</t>
-  </si>
-  <si>
-    <t>7(15:00)</t>
-  </si>
-  <si>
-    <t>8(16:00)</t>
-  </si>
-  <si>
-    <t>동아리</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -188,7 +193,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -204,19 +209,22 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -557,188 +565,148 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2">
-        <v>206</v>
-      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2">
-        <v>201</v>
-      </c>
-      <c r="D2" s="2">
-        <v>205</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="D2" s="2"/>
       <c r="E2" s="2">
-        <v>203</v>
-      </c>
-      <c r="F2" s="9"/>
+        <v>200</v>
+      </c>
+      <c r="F2" s="2">
+        <v>200</v>
+      </c>
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="8"/>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2">
+        <v>109</v>
+      </c>
+      <c r="D6" s="2">
+        <v>100</v>
+      </c>
+      <c r="E6" s="2">
+        <v>100</v>
+      </c>
+      <c r="F6" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="2">
+        <v>100</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="6"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2">
-        <v>206</v>
-      </c>
-      <c r="C4" s="2">
-        <v>201</v>
-      </c>
-      <c r="D4" s="2">
-        <v>205</v>
-      </c>
-      <c r="E4" s="2">
-        <v>203</v>
-      </c>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="8"/>
-      <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="2">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="8"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="2">
-        <v>107</v>
-      </c>
-      <c r="F8" s="2">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="8"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2">
-        <v>205</v>
-      </c>
-      <c r="C10" s="2">
-        <v>203</v>
-      </c>
-      <c r="D10" s="2">
-        <v>206</v>
-      </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="8"/>
-      <c r="B11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="2">
-        <v>205</v>
-      </c>
-      <c r="C12" s="2">
-        <v>203</v>
-      </c>
-      <c r="D12" s="2">
-        <v>206</v>
-      </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="5" t="s">
-        <v>16</v>
-      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="8"/>
-      <c r="B13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -748,7 +716,7 @@
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -757,16 +725,7 @@
       <c r="F15" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
+  <mergeCells count="12">
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="E12:E13"/>
@@ -774,9 +733,11 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/00.xlsx
+++ b/00.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61BAB51D-3CC0-4935-9D05-C300E55EB846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18AEAED-7EC6-48E9-AD6F-55F3A976A3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
+    <workbookView xWindow="31755" yWindow="3870" windowWidth="21600" windowHeight="11295" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>교시</t>
   </si>
@@ -60,27 +60,43 @@
     <t>8(16:00)</t>
   </si>
   <si>
+    <t>감독</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3(10:40)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4(11:50)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5(13:00)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공통영어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>화학2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>감독</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3(10:40)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>공통영어</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4(11:50)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>5(13:00)</t>
+    <t>공통국어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합사회</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>공통수학</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합과학</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -209,22 +225,22 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -565,7 +581,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2"/>
@@ -581,21 +597,21 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
+      <c r="A3" s="7"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>12</v>
+      <c r="F3" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2"/>
@@ -605,7 +621,7 @@
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
+      <c r="A5" s="7"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -613,96 +629,96 @@
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>13</v>
+      <c r="A6" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
         <v>109</v>
       </c>
       <c r="D6" s="2">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="E6" s="2">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F6" s="2">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6"/>
+      <c r="A7" s="7"/>
       <c r="B7" s="3"/>
-      <c r="C7" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>12</v>
+      <c r="C7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
+      <c r="A8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
       <c r="D8" s="2">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="10" t="s">
-        <v>12</v>
+      <c r="A9" s="7"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>16</v>
+      <c r="A10" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="9"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6"/>
+      <c r="A11" s="7"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="9"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6"/>
+      <c r="A13" s="7"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
@@ -726,6 +742,9 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="F10:F11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="E12:E13"/>
@@ -735,9 +754,6 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/00.xlsx
+++ b/00.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18AEAED-7EC6-48E9-AD6F-55F3A976A3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F67FCA2-8799-46FA-B61A-EB0C79F21D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31755" yWindow="3870" windowWidth="21600" windowHeight="11295" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
+    <workbookView xWindow="2310" yWindow="3600" windowWidth="21600" windowHeight="11295" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>교시</t>
   </si>
@@ -72,10 +72,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>5(13:00)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>공통영어</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -97,6 +93,14 @@
   </si>
   <si>
     <t>통합과학</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5(12:40)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>로비</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -600,7 +604,7 @@
       <c r="A3" s="7"/>
       <c r="B3" s="3"/>
       <c r="C3" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="5" t="s">
@@ -650,16 +654,16 @@
       <c r="A7" s="7"/>
       <c r="B7" s="3"/>
       <c r="C7" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -679,18 +683,20 @@
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
       <c r="E10" s="10"/>
       <c r="F10" s="8"/>
     </row>
@@ -698,7 +704,9 @@
       <c r="A11" s="7"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="D11" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
     </row>

--- a/00.xlsx
+++ b/00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F67FCA2-8799-46FA-B61A-EB0C79F21D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9D6F09-656D-4AA7-B3F2-F094C12DACC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2310" yWindow="3600" windowWidth="21600" windowHeight="11295" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
@@ -693,8 +693,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2">
+      <c r="C10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="10"/>
@@ -703,8 +702,7 @@
     <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7"/>
       <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="9"/>

--- a/00.xlsx
+++ b/00.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9D6F09-656D-4AA7-B3F2-F094C12DACC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D244CBE9-428F-444B-9912-089CB1B0F458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2310" yWindow="3600" windowWidth="21600" windowHeight="11295" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -96,11 +96,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>5(12:40)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>로비</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5(13:00)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -641,7 +641,7 @@
         <v>109</v>
       </c>
       <c r="D6" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E6" s="2">
         <v>109</v>
@@ -673,7 +673,7 @@
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
@@ -690,10 +690,11 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2"/>
-      <c r="C10" s="2">
+      <c r="C10" s="2"/>
+      <c r="D10">
         <v>0</v>
       </c>
       <c r="E10" s="10"/>
@@ -702,8 +703,9 @@
     <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7"/>
       <c r="B11" s="3"/>
-      <c r="C11" s="5" t="s">
-        <v>21</v>
+      <c r="C11" s="5"/>
+      <c r="D11" t="s">
+        <v>20</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>

--- a/00.xlsx
+++ b/00.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D244CBE9-428F-444B-9912-089CB1B0F458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4127BF-4597-4688-ABBD-B9FB89FEE15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="9.9999999974897903E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>교시</t>
   </si>
@@ -96,11 +96,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>로비</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>5(13:00)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>생명2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -594,7 +594,7 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2">
-        <v>200</v>
+        <v>301</v>
       </c>
       <c r="F2" s="2">
         <v>200</v>
@@ -608,7 +608,7 @@
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="5" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>11</v>
@@ -690,13 +690,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10">
-        <v>0</v>
-      </c>
       <c r="E10" s="10"/>
       <c r="F10" s="8"/>
     </row>
@@ -704,9 +701,6 @@
       <c r="A11" s="7"/>
       <c r="B11" s="3"/>
       <c r="C11" s="5"/>
-      <c r="D11" t="s">
-        <v>20</v>
-      </c>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
     </row>

--- a/00.xlsx
+++ b/00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4127BF-4597-4688-ABBD-B9FB89FEE15F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1AA74A-FC97-4137-A79A-F13E70AF4FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
@@ -60,10 +60,6 @@
     <t>8(16:00)</t>
   </si>
   <si>
-    <t>감독</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>3(10:40)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -101,6 +97,10 @@
   </si>
   <si>
     <t>생명2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>생명1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -597,21 +597,21 @@
         <v>301</v>
       </c>
       <c r="F2" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7"/>
       <c r="B3" s="3"/>
       <c r="C3" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -634,7 +634,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
@@ -647,28 +647,28 @@
         <v>109</v>
       </c>
       <c r="F6" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7"/>
       <c r="B7" s="3"/>
       <c r="C7" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
@@ -683,14 +683,14 @@
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>

--- a/00.xlsx
+++ b/00.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1AA74A-FC97-4137-A79A-F13E70AF4FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65003F5F-AA89-4966-9BFA-8CE328C8E5C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
   <si>
     <t>교시</t>
   </si>
@@ -60,47 +60,22 @@
     <t>8(16:00)</t>
   </si>
   <si>
-    <t>3(10:40)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4(11:50)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>공통영어</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>화학2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>공통국어</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>통합사회</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>공통수학</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>통합과학</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>역학</t>
+  </si>
+  <si>
+    <t>3(10:20)</t>
+  </si>
+  <si>
+    <t>4(11:20)</t>
+  </si>
+  <si>
+    <t>통과A</t>
   </si>
   <si>
     <t>5(13:00)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>생명2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>생명1</t>
+  </si>
+  <si>
+    <t>동아리</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -213,7 +188,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -227,9 +202,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -585,142 +557,184 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2">
+        <v>206</v>
+      </c>
       <c r="C2" s="2">
-        <v>302</v>
-      </c>
-      <c r="D2" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="D2" s="2">
+        <v>205</v>
+      </c>
       <c r="E2" s="2">
-        <v>301</v>
-      </c>
-      <c r="F2" s="2">
         <v>203</v>
       </c>
+      <c r="F2" s="9"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2">
+        <v>206</v>
+      </c>
+      <c r="C4" s="2">
+        <v>201</v>
+      </c>
+      <c r="D4" s="2">
+        <v>205</v>
+      </c>
+      <c r="E4" s="2">
+        <v>203</v>
+      </c>
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6"/>
+      <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="2">
+        <v>107</v>
+      </c>
+      <c r="F8" s="2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="7"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2">
-        <v>109</v>
-      </c>
-      <c r="D6" s="2">
-        <v>109</v>
-      </c>
-      <c r="E6" s="2">
-        <v>109</v>
-      </c>
-      <c r="F6" s="2">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="F9" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="2">
-        <v>108</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="5" t="s">
+      <c r="B10" s="2">
+        <v>205</v>
+      </c>
+      <c r="C10" s="2">
+        <v>203</v>
+      </c>
+      <c r="D10" s="2">
+        <v>206</v>
+      </c>
+      <c r="E10" s="9"/>
+      <c r="F10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="7"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="5"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="8"/>
+      <c r="B12" s="2">
+        <v>205</v>
+      </c>
+      <c r="C12" s="2">
+        <v>203</v>
+      </c>
+      <c r="D12" s="2">
+        <v>206</v>
+      </c>
+      <c r="E12" s="9"/>
+      <c r="F12" s="7" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="7"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
@@ -743,7 +757,10 @@
       <c r="F15" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="D8:D9"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A7"/>
@@ -756,6 +773,10 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
